--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64908_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64908_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf8e0fcc02a0d4c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1739fcaa6719481d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3334</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3151</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3230</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64908_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_64908_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1739fcaa6719481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R54f71d0066d24c55"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5124</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8039</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9912</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4232</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2869</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3223</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2987</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.6293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4471</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9831</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3578</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2253</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3793</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3771</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3115</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2869</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5703</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5826</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5821</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7828</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3334</x:v>
+        <x:v>      3.3967</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6158</x:v>
+        <x:v>      2.6954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.8254</x:v>
+        <x:v>      5.8422</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.3110</x:v>
+        <x:v>      6.2987</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4308</x:v>
+        <x:v>      6.4168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.3151</x:v>
+        <x:v>      6.2253</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.3553</x:v>
+        <x:v>      6.3423</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.3990</x:v>
+        <x:v>      6.3855</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.3230</x:v>
+        <x:v>      6.3105</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.3230</x:v>
+        <x:v>      6.3105</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7259</x:v>
+        <x:v>      5.7437</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.6821</x:v>
+        <x:v>      5.7017</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5043</x:v>
+        <x:v>      3.5637</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5470</x:v>
+        <x:v>      3.6054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6496</x:v>
+        <x:v>      3.7056</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5726</x:v>
+        <x:v>      3.6305</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7521</x:v>
+        <x:v>      3.8058</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2647</x:v>
+        <x:v>      4.3067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2825</x:v>
+        <x:v>      4.3241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2647</x:v>
+        <x:v>      4.3067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4014</x:v>
+        <x:v>      4.4403</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9225</x:v>
+        <x:v>      4.9497</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1361</x:v>
+        <x:v>      5.1583</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4495</x:v>
+        <x:v>      5.4783</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.5034</x:v>
+        <x:v>      5.5174</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.6016</x:v>
+        <x:v>      5.6497</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1991</x:v>
+        <x:v>      6.1883</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5146</x:v>
+        <x:v>      6.4995</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6223</x:v>
+        <x:v>      6.6057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8139</x:v>
+        <x:v>      6.7946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0893</x:v>
+        <x:v>      7.0662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.4964</x:v>
+        <x:v>      7.4676</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.7478</x:v>
+        <x:v>      7.7156</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.5922</x:v>
+        <x:v>      7.5621</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5924</x:v>
+        <x:v>      6.5762</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6463</x:v>
+        <x:v>      6.6293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6603</x:v>
+        <x:v>      6.6270</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5325</x:v>
+        <x:v>      6.5172</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5026</x:v>
+        <x:v>      6.4876</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5984</x:v>
+        <x:v>      6.5821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6822</x:v>
+        <x:v>      6.6648</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5984</x:v>
+        <x:v>      6.5821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6583</x:v>
+        <x:v>      6.6412</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5984</x:v>
+        <x:v>      6.5821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6343</x:v>
+        <x:v>      6.6175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5265</x:v>
+        <x:v>      6.5113</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5505</x:v>
+        <x:v>      6.5349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5984</x:v>
+        <x:v>      6.5821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6104</x:v>
+        <x:v>      6.5939</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6223</x:v>
+        <x:v>      6.6057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6583</x:v>
+        <x:v>      6.6412</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6223</x:v>
+        <x:v>      6.6057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6489</x:v>
+        <x:v>      6.6319</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6223</x:v>
+        <x:v>      6.6057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5989</x:v>
+        <x:v>      6.5826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6942</x:v>
+        <x:v>      6.6766</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5926</x:v>
+        <x:v>      6.5765</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6942</x:v>
+        <x:v>      6.6766</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.9456</x:v>
+        <x:v>      6.9245</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.9935</x:v>
+        <x:v>      6.9717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.9935</x:v>
+        <x:v>      6.9717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0414</x:v>
+        <x:v>      7.0190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.9425</x:v>
+        <x:v>      6.9215</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8379</x:v>
+        <x:v>      6.8183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8601</x:v>
+        <x:v>      6.8402</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8499</x:v>
+        <x:v>      6.8301</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8618</x:v>
+        <x:v>      6.8419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8379</x:v>
+        <x:v>      6.8183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8738</x:v>
+        <x:v>      6.8537</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8379</x:v>
+        <x:v>      6.8183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8607</x:v>
+        <x:v>      6.8408</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8618</x:v>
+        <x:v>      6.8419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8379</x:v>
+        <x:v>      6.8183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8738</x:v>
+        <x:v>      6.8537</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8738</x:v>
+        <x:v>      6.8537</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3235</x:v>
+        <x:v>      7.2972</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.9456</x:v>
+        <x:v>      6.9245</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1252</x:v>
+        <x:v>      7.1016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1611</x:v>
+        <x:v>      7.1370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6104</x:v>
+        <x:v>      6.5939</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6463</x:v>
+        <x:v>      6.6293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6942</x:v>
+        <x:v>      6.6766</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5984</x:v>
+        <x:v>      6.5821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5989</x:v>
+        <x:v>      6.5826</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5864</x:v>
+        <x:v>      6.5703</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6223</x:v>
+        <x:v>      6.6057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5984</x:v>
+        <x:v>      6.5821</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.6223</x:v>
+        <x:v>      6.6057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.5796</x:v>
+        <x:v>      6.5636</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8738</x:v>
+        <x:v>      6.8537</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1611</x:v>
+        <x:v>      7.1370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1611</x:v>
+        <x:v>      7.1370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0414</x:v>
+        <x:v>      7.0190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0653</x:v>
+        <x:v>      7.0426</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1611</x:v>
+        <x:v>      7.1370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0893</x:v>
+        <x:v>      7.0662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1611</x:v>
+        <x:v>      7.1370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2236</x:v>
+        <x:v>      7.1986</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1611</x:v>
+        <x:v>      7.1370</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0773</x:v>
+        <x:v>      7.0544</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7541</x:v>
+        <x:v>      6.7356</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7181</x:v>
+        <x:v>      6.7002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8139</x:v>
+        <x:v>      6.7946</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0055</x:v>
+        <x:v>      6.9836</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.4125</x:v>
+        <x:v>      7.3850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.4006</x:v>
+        <x:v>      7.3732</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.7358</x:v>
+        <x:v>      7.7038</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7895</x:v>
+        <x:v>      8.7429</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.1908</x:v>
+        <x:v>      8.1525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.5802</x:v>
+        <x:v>      7.5503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2449</x:v>
+        <x:v>      7.2197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2210</x:v>
+        <x:v>      7.1961</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4547</x:v>
+        <x:v>      6.4404</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8114</x:v>
+        <x:v>      4.8411</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2087</x:v>
+        <x:v>      4.2521</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8501</x:v>
+        <x:v>      3.9016</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4831</x:v>
+        <x:v>      4.5202</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.3628</x:v>
+        <x:v>      5.3881</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4732</x:v>
+        <x:v>      5.5038</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.3934</x:v>
+        <x:v>      5.4189</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8618</x:v>
+        <x:v>      6.8419</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.0072</x:v>
+        <x:v>      9.9772</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.6921</x:v>
+        <x:v>      8.6503</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.0326</x:v>
+        <x:v>     13.0263</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5252</x:v>
+        <x:v>     11.5111</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.3274</x:v>
+        <x:v>     11.3006</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7103</x:v>
+        <x:v>      8.6649</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.5672</x:v>
+        <x:v>      7.5375</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.5922</x:v>
+        <x:v>      7.5621</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2330</x:v>
+        <x:v>      7.2079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1970</x:v>
+        <x:v>      7.1725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3407</x:v>
+        <x:v>      7.3141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8585</x:v>
+        <x:v>      4.8849</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2395</x:v>
+        <x:v>      3.3048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5300</x:v>
+        <x:v>      3.5887</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5470</x:v>
+        <x:v>      3.6054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6496</x:v>
+        <x:v>      3.7056</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7493</x:v>
+        <x:v>      5.7561</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3287</x:v>
+        <x:v>      7.3024</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.0914</x:v>
+        <x:v>     10.0337</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4349</x:v>
+        <x:v>      9.3795</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.5557</x:v>
+        <x:v>      9.4986</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.5349</x:v>
+        <x:v>      9.4780</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.8972</x:v>
+        <x:v>      8.8491</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7655</x:v>
+        <x:v>      8.7193</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +3534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.0726</x:v>
+        <x:v>      9.0222</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +3549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1486</x:v>
+        <x:v>      9.0971</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +3564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1150</x:v>
+        <x:v>      4.1619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2395</x:v>
+        <x:v>      3.3048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5470</x:v>
+        <x:v>      3.6054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0596</x:v>
+        <x:v>      4.1064</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +3624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.6064</x:v>
+        <x:v>      4.6407</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +3639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8627</x:v>
+        <x:v>      4.8912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1446</x:v>
+        <x:v>      5.1667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.1443</x:v>
+        <x:v>      6.1519</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.8733</x:v>
+        <x:v>      8.8255</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.8443</x:v>
+        <x:v>     14.8413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7074</x:v>
+        <x:v>     11.6820</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3009,7 +3729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.6458</x:v>
+        <x:v>      8.6012</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3024,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7114</x:v>
+        <x:v>      9.6521</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3114,7 +3834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     15.2661</x:v>
+        <x:v>     15.2493</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +3849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8725</x:v>
+        <x:v>      6.8611</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +3864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.9747</x:v>
+        <x:v>      5.9760</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +3879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.4930</x:v>
+        <x:v>      5.5332</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +3894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.2007</x:v>
+        <x:v>      5.2215</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +3909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.3642</x:v>
+        <x:v>      6.3638</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3204,7 +3924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.9362</x:v>
+        <x:v>      6.9153</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3219,7 +3939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6209</x:v>
+        <x:v>      7.5904</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3264,7 +3984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9873</x:v>
+        <x:v>      7.9518</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3279,7 +3999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1251</x:v>
+        <x:v>     12.1071</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3354,7 +4074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     16.0706</x:v>
+        <x:v>     16.0422</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3369,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.0346</x:v>
+        <x:v>      9.9709</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3384,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.5568</x:v>
+        <x:v>     10.5050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3399,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.5070</x:v>
+        <x:v>     13.4901</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3414,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.6571</x:v>
+        <x:v>     12.6432</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3429,7 +4149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.6479</x:v>
+        <x:v>     10.6140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.5568</x:v>
+        <x:v>     10.5050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +4239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.2382</x:v>
+        <x:v>     12.2213</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +4254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4542</x:v>
+        <x:v>      8.4123</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +4269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3048</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +4284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.4972</x:v>
+        <x:v>      6.4994</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +4299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.7638</x:v>
+        <x:v>      5.7684</x:v>
       </x:c>
     </x:row>
     <x:row>
